--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,138 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124981602</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Krontorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>477666</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6600980</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124889209</v>
+        <v>124891120</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,58 +818,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477718</v>
+        <v>477776</v>
       </c>
       <c r="R3" t="n">
-        <v>6601046</v>
+        <v>6600931</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124891120</v>
+        <v>124889209</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>57519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,38 +930,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477776</v>
+        <v>477718</v>
       </c>
       <c r="R4" t="n">
-        <v>6600931</v>
+        <v>6601046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124888486</v>
+        <v>124891120</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,57 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477736</v>
+        <v>477776</v>
       </c>
       <c r="R2" t="n">
-        <v>6601007</v>
+        <v>6600931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124891120</v>
+        <v>124889209</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>57519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,38 +799,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477776</v>
+        <v>477718</v>
       </c>
       <c r="R3" t="n">
-        <v>6600931</v>
+        <v>6601046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124889209</v>
+        <v>124888486</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,20 +969,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477718</v>
+        <v>477736</v>
       </c>
       <c r="R4" t="n">
-        <v>6601046</v>
+        <v>6601007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124889209</v>
+        <v>124888486</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,20 +837,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477718</v>
+        <v>477736</v>
       </c>
       <c r="R3" t="n">
-        <v>6601046</v>
+        <v>6601007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124888486</v>
+        <v>124889209</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,19 +968,20 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477736</v>
+        <v>477718</v>
       </c>
       <c r="R4" t="n">
-        <v>6601007</v>
+        <v>6601046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124888486</v>
+        <v>124981602</v>
       </c>
       <c r="B3" t="n">
         <v>57666</v>
@@ -840,16 +840,17 @@
           <t>par i lämplig häckbiotop</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477736</v>
+        <v>477666</v>
       </c>
       <c r="R3" t="n">
-        <v>6601007</v>
+        <v>6600980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,22 +877,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,14 +919,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124889209</v>
+        <v>124888486</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -934,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,20 +969,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477718</v>
+        <v>477736</v>
       </c>
       <c r="R4" t="n">
-        <v>6601046</v>
+        <v>6601007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,14 +1050,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124981602</v>
+        <v>124889209</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1066,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1100,20 +1100,20 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477666</v>
+        <v>477718</v>
       </c>
       <c r="R5" t="n">
-        <v>6600980</v>
+        <v>6601046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,22 +1140,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124888486</v>
+        <v>124889209</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,19 +969,20 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477736</v>
+        <v>477718</v>
       </c>
       <c r="R4" t="n">
-        <v>6601007</v>
+        <v>6601046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124889209</v>
+        <v>124888486</v>
       </c>
       <c r="B5" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,21 +1067,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1100,20 +1101,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477718</v>
+        <v>477736</v>
       </c>
       <c r="R5" t="n">
-        <v>6601046</v>
+        <v>6601007</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -787,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981602</v>
+        <v>124889209</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,20 +837,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477666</v>
+        <v>477718</v>
       </c>
       <c r="R3" t="n">
-        <v>6600980</v>
+        <v>6601046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,22 +877,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124889209</v>
+        <v>124888486</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,20 +969,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477718</v>
+        <v>477736</v>
       </c>
       <c r="R4" t="n">
-        <v>6601046</v>
+        <v>6601007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124888486</v>
+        <v>124981602</v>
       </c>
       <c r="B5" t="n">
         <v>57666</v>
@@ -1104,16 +1103,17 @@
           <t>par i lämplig häckbiotop</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477736</v>
+        <v>477666</v>
       </c>
       <c r="R5" t="n">
-        <v>6601007</v>
+        <v>6600980</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,22 +1140,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124888486</v>
+        <v>124889209</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,19 +837,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477736</v>
+        <v>477718</v>
       </c>
       <c r="R3" t="n">
-        <v>6601007</v>
+        <v>6601046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124889209</v>
+        <v>124888486</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,20 +969,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477718</v>
+        <v>477736</v>
       </c>
       <c r="R4" t="n">
-        <v>6601046</v>
+        <v>6601007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124891120</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124888486</v>
+        <v>124889209</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57648</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,19 +837,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477736</v>
+        <v>477718</v>
       </c>
       <c r="R3" t="n">
-        <v>6601007</v>
+        <v>6601046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124889209</v>
+        <v>124888486</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,20 +969,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477718</v>
+        <v>477736</v>
       </c>
       <c r="R4" t="n">
-        <v>6601046</v>
+        <v>6601007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1053,7 @@
         <v>124981602</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124889209</v>
+        <v>124888486</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>57793</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,20 +837,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477718</v>
+        <v>477736</v>
       </c>
       <c r="R3" t="n">
-        <v>6601046</v>
+        <v>6601007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124888486</v>
+        <v>124889209</v>
       </c>
       <c r="B4" t="n">
-        <v>57793</v>
+        <v>57648</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,19 +968,20 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477736</v>
+        <v>477718</v>
       </c>
       <c r="R4" t="n">
-        <v>6601007</v>
+        <v>6601046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20238-2021 artfynd.xlsx
+++ b/artfynd/A 20238-2021 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>80057</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>LC</t>
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124888486</v>
+        <v>124889209</v>
       </c>
       <c r="B3" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57664</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,19 +827,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477736</v>
+        <v>477718</v>
       </c>
       <c r="R3" t="n">
-        <v>6601007</v>
+        <v>6601046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124889209</v>
+        <v>124888486</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,20 +954,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477718</v>
+        <v>477736</v>
       </c>
       <c r="R4" t="n">
-        <v>6601046</v>
+        <v>6601007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,12 +1038,7 @@
         <v>124981602</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
